--- a/Evaluation.xlsx
+++ b/Evaluation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kim_W\Ekkono_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992EB966-EE88-4353-B3AB-0411406AEB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79424D96-CB7E-42F1-9F13-A0874E3322E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
   </bookViews>
@@ -175,7 +175,7 @@
     <t>input_length_tokens</t>
   </si>
   <si>
-    <t>duration_tokens</t>
+    <t>duration_seconds</t>
   </si>
 </sst>
 </file>
@@ -263,7 +263,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -280,7 +280,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -616,7 +615,7 @@
     <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -651,29 +650,29 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
       <c r="E2">
         <v>3924</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2">
         <v>48.55</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2">
         <f>'d131 #1'!F3</f>
         <v>3.6500000000000004</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2">
         <v>3.5</v>
       </c>
       <c r="I2">
@@ -682,29 +681,29 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3">
         <v>8866</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3">
         <v>60.65</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3">
         <f>'d131 #1'!F4</f>
         <v>3.65</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3">
         <v>3.65</v>
       </c>
       <c r="I3">
@@ -713,29 +712,29 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" t="s">
         <v>6</v>
       </c>
       <c r="E4">
         <v>9097</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4">
         <v>59.3</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4">
         <f>'d131 #1'!F5</f>
         <v>3.3000000000000003</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4">
         <v>3.3</v>
       </c>
       <c r="I4">
@@ -744,29 +743,29 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" t="s">
         <v>4</v>
       </c>
       <c r="E5">
         <v>2669</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5">
         <v>66.599999999999994</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5">
         <f>'d131 #1'!F6</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5">
         <v>2.5</v>
       </c>
       <c r="I5">
@@ -775,29 +774,29 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6">
         <v>5601</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6">
         <v>206.04</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6">
         <f>'d131 #1'!F7</f>
         <v>3.65</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6">
         <v>3.3</v>
       </c>
       <c r="I6">
@@ -806,29 +805,29 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7">
         <v>5743</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7">
         <v>116.24</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7">
         <f>'d131 #1'!F8</f>
         <v>3.4</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7">
         <v>3.3</v>
       </c>
       <c r="I7">
@@ -837,29 +836,29 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" t="s">
         <v>4</v>
       </c>
       <c r="E8">
         <v>2669</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8">
         <v>24.46</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8">
         <f>'d131 #1'!F9</f>
         <v>3.3000000000000003</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8">
         <v>3.3</v>
       </c>
       <c r="I8">
@@ -868,29 +867,29 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" t="s">
         <v>5</v>
       </c>
       <c r="E9">
         <v>5566</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9">
         <v>26.88</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9">
         <f>'d131 #1'!F10</f>
         <v>3.2499999999999996</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9">
         <v>3.05</v>
       </c>
       <c r="I9">
@@ -899,29 +898,29 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" t="s">
         <v>6</v>
       </c>
       <c r="E10">
         <v>5705</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10">
         <v>24.95</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10">
         <f>'d131 #1'!F11</f>
         <v>3.4</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10">
         <v>3.3</v>
       </c>
       <c r="I10">
@@ -930,109 +929,109 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" t="s">
         <v>4</v>
       </c>
       <c r="E11">
         <v>1927</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11">
         <v>43.72</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11">
         <f>'d393 #1'!F3</f>
         <v>4.3499999999999996</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11">
         <v>4.7</v>
       </c>
       <c r="I11">
-        <f xml:space="preserve"> ABS(H11-G11)</f>
+        <f t="shared" ref="I11:I19" si="1" xml:space="preserve"> ABS(H11-G11)</f>
         <v>0.35000000000000053</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" t="s">
         <v>5</v>
       </c>
       <c r="E12">
         <v>4317</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12">
         <v>72.33</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12">
         <f>'d393 #1'!F4</f>
         <v>4.2</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12">
         <v>4.2</v>
       </c>
       <c r="I12">
-        <f xml:space="preserve"> ABS(H12-G12)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" t="s">
         <v>6</v>
       </c>
       <c r="E13">
         <v>4547</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13">
         <v>57.89</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13">
         <f>'d393 #1'!F5</f>
         <v>4.2</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13">
         <v>4.0999999999999996</v>
       </c>
       <c r="I13">
-        <f xml:space="preserve"> ABS(H13-G13)</f>
+        <f t="shared" si="1"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" t="s">
         <v>4</v>
       </c>
       <c r="E14">
@@ -1041,29 +1040,29 @@
       <c r="F14">
         <v>97.2</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14">
         <f>'d393 #1'!F6</f>
         <v>3.5500000000000003</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14">
         <v>3.8</v>
       </c>
       <c r="I14">
-        <f xml:space="preserve"> ABS(H14-G14)</f>
+        <f t="shared" si="1"/>
         <v>0.24999999999999956</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15">
@@ -1072,29 +1071,29 @@
       <c r="F15">
         <v>116.94</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15">
         <f>'d393 #1'!F7</f>
         <v>3.9000000000000004</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15">
         <v>3.9</v>
       </c>
       <c r="I15">
-        <f xml:space="preserve"> ABS(H15-G15)</f>
+        <f t="shared" si="1"/>
         <v>4.4408920985006262E-16</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" t="s">
         <v>6</v>
       </c>
       <c r="E16">
@@ -1103,29 +1102,29 @@
       <c r="F16">
         <v>121.81</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16">
         <f>'d393 #1'!F8</f>
         <v>4.55</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16">
         <v>4.5999999999999996</v>
       </c>
       <c r="I16">
-        <f xml:space="preserve"> ABS(H16-G16)</f>
+        <f t="shared" si="1"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" t="s">
         <v>4</v>
       </c>
       <c r="E17">
@@ -1134,29 +1133,29 @@
       <c r="F17">
         <v>28.43</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17">
         <f>'d393 #1'!F9</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17">
         <v>4.0999999999999996</v>
       </c>
       <c r="I17">
-        <f xml:space="preserve"> ABS(H17-G17)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18">
@@ -1165,29 +1164,29 @@
       <c r="F18">
         <v>11.72</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18">
         <f>'d393 #1'!F10</f>
         <v>3.9499999999999997</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18">
         <v>3.85</v>
       </c>
       <c r="I18">
-        <f xml:space="preserve"> ABS(H18-G18)</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999645E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" t="s">
         <v>6</v>
       </c>
       <c r="E19">
@@ -1196,42 +1195,42 @@
       <c r="F19">
         <v>27.51</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19">
         <f>'d393 #1'!F11</f>
         <v>3.9</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19">
         <v>3.8</v>
       </c>
       <c r="I19">
-        <f xml:space="preserve"> ABS(H19-G19)</f>
+        <f t="shared" si="1"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" t="s">
         <v>4</v>
       </c>
       <c r="E20">
         <v>3930</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20">
         <v>60.04</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20">
         <f>'d1456 #1'!F3</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20">
         <v>4.0999999999999996</v>
       </c>
       <c r="I20">
@@ -1240,29 +1239,29 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21">
         <v>8680</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21">
         <v>55.56</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21">
         <f>'d1456 #1'!F4</f>
         <v>4.2</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21">
         <v>4.2</v>
       </c>
       <c r="I21">
@@ -1271,29 +1270,29 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" t="s">
         <v>6</v>
       </c>
       <c r="E22">
         <v>8914</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22">
         <v>67</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22">
         <f>'d1456 #1'!F5</f>
         <v>3.9</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22">
         <v>4.1500000000000004</v>
       </c>
       <c r="I22">
@@ -1302,29 +1301,29 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23">
         <v>2668</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23">
         <v>86.88</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23">
         <f>'d1456 #1'!F6</f>
         <v>3.6500000000000004</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23">
         <v>3.9</v>
       </c>
       <c r="I23">
@@ -1333,29 +1332,29 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="A24" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24">
         <v>5480</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24">
         <v>92.22</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24">
         <f>'d1456 #1'!F7</f>
         <v>3.45</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24">
         <v>3.55</v>
       </c>
       <c r="I24">
@@ -1364,29 +1363,29 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
+      <c r="A25" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" t="s">
         <v>6</v>
       </c>
       <c r="E25">
         <v>5622</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25">
         <v>82.61</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25">
         <f>'d1456 #1'!F8</f>
         <v>3.8000000000000003</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25">
         <v>3.85</v>
       </c>
       <c r="I25">
@@ -1395,29 +1394,29 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
+      <c r="A26" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" t="s">
         <v>4</v>
       </c>
       <c r="E26">
         <v>2670</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26">
         <v>21.64</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26">
         <f>'d1456 #1'!F9</f>
         <v>3.65</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26">
         <v>3.55</v>
       </c>
       <c r="I26">
@@ -1426,29 +1425,29 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
+      <c r="A27" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" t="s">
         <v>5</v>
       </c>
       <c r="E27">
         <v>5450</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27">
         <v>34.479999999999997</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27">
         <f>'d1456 #1'!F10</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27">
         <v>4.0999999999999996</v>
       </c>
       <c r="I27">
@@ -1457,29 +1456,29 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
+      <c r="A28" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" t="s">
         <v>6</v>
       </c>
       <c r="E28">
         <v>5589</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28">
         <v>46.06</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28">
         <f>'d1456 #1'!F11</f>
         <v>3.8499999999999996</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28">
         <v>3.85</v>
       </c>
       <c r="I28">
@@ -1488,29 +1487,29 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
+      <c r="A29" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" t="s">
         <v>4</v>
       </c>
       <c r="E29">
         <v>3929</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29">
         <v>52.85</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29">
         <f>'d3235 #1'!F3</f>
         <v>3.75</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29">
         <v>3.85</v>
       </c>
       <c r="I29">
@@ -1519,29 +1518,29 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
+      <c r="A30" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" t="s">
         <v>5</v>
       </c>
       <c r="E30">
         <v>8653</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30">
         <v>63.44</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30">
         <f>'d3235 #1'!F4</f>
         <v>4.2</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30">
         <v>4.1500000000000004</v>
       </c>
       <c r="I30">
@@ -1550,29 +1549,29 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
+      <c r="A31" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" t="s">
         <v>6</v>
       </c>
       <c r="E31">
         <v>8888</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31">
         <v>64.31</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31">
         <f>'d3235 #1'!F5</f>
         <v>3.9</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31">
         <v>3.8</v>
       </c>
       <c r="I31">
@@ -1581,29 +1580,29 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
+      <c r="A32" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" t="s">
         <v>4</v>
       </c>
       <c r="E32">
         <v>2670</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32">
         <v>87.94</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32">
         <f>'d3235 #1'!F6</f>
         <v>3.9999999999999996</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32">
         <v>4.25</v>
       </c>
       <c r="I32">
@@ -1612,29 +1611,29 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
+      <c r="A33" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" t="s">
         <v>5</v>
       </c>
       <c r="E33">
         <v>5486</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33">
         <v>50.65</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33">
         <f>'d3235 #1'!F7</f>
         <v>3.8000000000000003</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33">
         <v>3.8</v>
       </c>
       <c r="I33">
@@ -1643,29 +1642,29 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" t="s">
         <v>6</v>
       </c>
       <c r="E34">
         <v>5628</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34">
         <v>106.3</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34">
         <f>'d3235 #1'!F8</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34">
         <v>4.0999999999999996</v>
       </c>
       <c r="I34">
@@ -1674,29 +1673,29 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+      <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" t="s">
         <v>4</v>
       </c>
       <c r="E35">
         <v>2671</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35">
         <v>37.19</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35">
         <f>'d3235 #1'!F9</f>
         <v>4.5500000000000007</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35">
         <v>4.55</v>
       </c>
       <c r="I35">
@@ -1705,29 +1704,29 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
+      <c r="A36" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" t="s">
         <v>22</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" t="s">
         <v>5</v>
       </c>
       <c r="E36">
         <v>5456</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36">
         <v>89.83</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36">
         <f>'d3235 #1'!F10</f>
         <v>3.9499999999999997</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36">
         <v>3.85</v>
       </c>
       <c r="I36">
@@ -1736,29 +1735,29 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
+      <c r="A37" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" t="s">
         <v>6</v>
       </c>
       <c r="E37">
         <v>5595</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37">
         <v>50.28</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37">
         <f>'d3235 #1'!F11</f>
         <v>3.4</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37">
         <v>3.3</v>
       </c>
       <c r="I37">
@@ -1767,308 +1766,308 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="10" t="s">
+      <c r="A38" t="s">
         <v>16</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" t="s">
         <v>23</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" t="s">
         <v>4</v>
       </c>
       <c r="E38">
         <v>4296</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38">
         <v>64.09</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38">
         <f>'d131 #2'!F3</f>
         <v>2.95</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38">
         <v>2.85</v>
       </c>
       <c r="I38">
-        <f xml:space="preserve"> ABS(H38-G38)</f>
+        <f t="shared" ref="I38:I46" si="2" xml:space="preserve"> ABS(H38-G38)</f>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="10" t="s">
+      <c r="A39" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" t="s">
         <v>5</v>
       </c>
       <c r="E39">
         <v>12637</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39">
         <v>59.2</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39">
         <f>'d131 #2'!F4</f>
         <v>3.6500000000000004</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39">
         <v>3.65</v>
       </c>
       <c r="I39">
-        <f xml:space="preserve"> ABS(H39-G39)</f>
+        <f t="shared" si="2"/>
         <v>4.4408920985006262E-16</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="10" t="s">
+      <c r="A40" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" t="s">
         <v>23</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" t="s">
         <v>6</v>
       </c>
       <c r="E40">
         <v>14036</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40">
         <v>65.959999999999994</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40">
         <f>'d131 #2'!F5</f>
         <v>3.9</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40">
         <v>4</v>
       </c>
       <c r="I40">
-        <f xml:space="preserve"> ABS(H40-G40)</f>
+        <f t="shared" si="2"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="10" t="s">
+      <c r="A41" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" t="s">
         <v>4</v>
       </c>
       <c r="E41">
         <v>3412</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41">
         <v>63.83</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41">
         <f>'d131 #2'!F6</f>
         <v>4</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41">
         <v>3.9</v>
       </c>
       <c r="I41">
-        <f xml:space="preserve"> ABS(H41-G41)</f>
+        <f t="shared" si="2"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
+      <c r="A42" t="s">
         <v>16</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" t="s">
         <v>23</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" t="s">
         <v>5</v>
       </c>
       <c r="E42">
         <v>9998</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42">
         <v>54.91</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42">
         <f>'d131 #2'!F7</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42">
         <v>4.25</v>
       </c>
       <c r="I42">
-        <f xml:space="preserve"> ABS(H42-G42)</f>
+        <f t="shared" si="2"/>
         <v>0.15000000000000036</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="10" t="s">
+      <c r="A43" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" t="s">
         <v>6</v>
       </c>
       <c r="E43">
         <v>10853</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43">
         <v>131.18</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43">
         <f>'d131 #2'!F8</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43">
         <v>4.2</v>
       </c>
       <c r="I43">
-        <f xml:space="preserve"> ABS(H43-G43)</f>
+        <f t="shared" si="2"/>
         <v>8.8817841970012523E-16</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="10" t="s">
+      <c r="A44" t="s">
         <v>16</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" t="s">
         <v>4</v>
       </c>
       <c r="E44">
         <v>3346</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44">
         <v>29.02</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44">
         <f>'d131 #2'!F9</f>
         <v>3.65</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44">
         <v>3.55</v>
       </c>
       <c r="I44">
-        <f xml:space="preserve"> ABS(H44-G44)</f>
+        <f t="shared" si="2"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="10" t="s">
+      <c r="A45" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" t="s">
         <v>23</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45">
         <v>9689</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45">
         <v>47.76</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45">
         <f>'d131 #2'!F10</f>
         <v>4.3</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45">
         <v>4.25</v>
       </c>
       <c r="I45">
-        <f xml:space="preserve"> ABS(H45-G45)</f>
+        <f t="shared" si="2"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="10" t="s">
+      <c r="A46" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" t="s">
         <v>23</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" t="s">
         <v>6</v>
       </c>
       <c r="E46">
         <v>10521</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46">
         <v>39.33</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46">
         <f>'d131 #2'!F11</f>
         <v>3.5500000000000003</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46">
         <v>3.55</v>
       </c>
       <c r="I46">
-        <f xml:space="preserve"> ABS(H46-G46)</f>
+        <f t="shared" si="2"/>
         <v>4.4408920985006262E-16</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="10" t="s">
+      <c r="A47" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" t="s">
         <v>23</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" t="s">
         <v>4</v>
       </c>
       <c r="E47">
         <v>3612</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47">
         <v>172.93</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47">
         <f>'d393 #2'!F3</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47">
         <v>4.2</v>
       </c>
       <c r="I47">
@@ -2077,29 +2076,29 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="10" t="s">
+      <c r="A48" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" t="s">
         <v>19</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" t="s">
         <v>23</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48">
         <v>9140</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48">
         <v>277.33999999999997</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48">
         <f>'d393 #2'!F4</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48">
         <v>4.2</v>
       </c>
       <c r="I48">
@@ -2108,29 +2107,29 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="10" t="s">
+      <c r="A49" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" t="s">
         <v>23</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" t="s">
         <v>6</v>
       </c>
       <c r="E49">
         <v>10298</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49">
         <v>126.77</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49">
         <f>'d393 #2'!F5</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="H49" s="10">
+      <c r="H49">
         <v>4.25</v>
       </c>
       <c r="I49">
@@ -2139,29 +2138,29 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
+      <c r="A50" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" t="s">
         <v>23</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" t="s">
         <v>4</v>
       </c>
       <c r="E50">
         <v>2903</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50">
         <v>86.28</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50">
         <f>'d393 #2'!F6</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50">
         <v>4.25</v>
       </c>
       <c r="I50">
@@ -2170,29 +2169,29 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="10" t="s">
+      <c r="A51" t="s">
         <v>33</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" t="s">
         <v>20</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" t="s">
         <v>23</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51">
         <v>7275</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51">
         <v>169.79</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51">
         <f>'d393 #2'!F7</f>
         <v>3.9</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51">
         <v>4.0999999999999996</v>
       </c>
       <c r="I51">
@@ -2201,29 +2200,29 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="10" t="s">
+      <c r="A52" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" t="s">
         <v>20</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" t="s">
         <v>6</v>
       </c>
       <c r="E52">
         <v>7985</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52">
         <v>164.39</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52">
         <f>'d393 #2'!F8</f>
         <v>4.6999999999999993</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52">
         <v>4.7</v>
       </c>
       <c r="I52">
@@ -2232,29 +2231,29 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="10" t="s">
+      <c r="A53" t="s">
         <v>33</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" t="s">
         <v>21</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" t="s">
         <v>23</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" t="s">
         <v>4</v>
       </c>
       <c r="E53">
         <v>2841</v>
       </c>
-      <c r="F53" s="10">
+      <c r="F53">
         <v>24.02</v>
       </c>
-      <c r="G53" s="10">
+      <c r="G53">
         <f>'d393 #2'!F9</f>
         <v>4.5500000000000007</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53">
         <v>4.55</v>
       </c>
       <c r="I53">
@@ -2263,29 +2262,29 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="10" t="s">
+      <c r="A54" t="s">
         <v>33</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" t="s">
         <v>5</v>
       </c>
       <c r="E54">
         <v>7025</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F54">
         <v>43.89</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G54">
         <f>'d393 #2'!F10</f>
         <v>3.8499999999999996</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54">
         <v>3.85</v>
       </c>
       <c r="I54">
@@ -2294,29 +2293,29 @@
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="10" t="s">
+      <c r="A55" t="s">
         <v>33</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" t="s">
         <v>23</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" t="s">
         <v>6</v>
       </c>
       <c r="E55">
         <v>7716</v>
       </c>
-      <c r="F55" s="10">
+      <c r="F55">
         <v>35.56</v>
       </c>
-      <c r="G55" s="10">
+      <c r="G55">
         <f>'d393 #2'!F11</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="H55" s="10">
+      <c r="H55">
         <v>4.4000000000000004</v>
       </c>
       <c r="I55">
@@ -2325,29 +2324,29 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="10" t="s">
+      <c r="A56" t="s">
         <v>18</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" t="s">
         <v>23</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" t="s">
         <v>4</v>
       </c>
       <c r="E56">
         <v>3764</v>
       </c>
-      <c r="F56" s="10">
+      <c r="F56">
         <v>135.57</v>
       </c>
-      <c r="G56" s="10">
+      <c r="G56">
         <f>'d1456 #2'!F3</f>
         <v>3.9000000000000004</v>
       </c>
-      <c r="H56" s="10">
+      <c r="H56">
         <v>4.05</v>
       </c>
       <c r="I56">
@@ -2356,29 +2355,29 @@
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="10" t="s">
+      <c r="A57" t="s">
         <v>18</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" t="s">
         <v>23</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" t="s">
         <v>5</v>
       </c>
       <c r="E57">
         <v>9712</v>
       </c>
-      <c r="F57" s="10">
+      <c r="F57">
         <v>140.74</v>
       </c>
-      <c r="G57" s="10">
+      <c r="G57">
         <f>'d1456 #2'!F4</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H57" s="10">
+      <c r="H57">
         <v>4.1500000000000004</v>
       </c>
       <c r="I57">
@@ -2387,29 +2386,29 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="10" t="s">
+      <c r="A58" t="s">
         <v>18</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" t="s">
         <v>23</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" t="s">
         <v>6</v>
       </c>
       <c r="E58">
         <v>10888</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F58">
         <v>119.63</v>
       </c>
-      <c r="G58" s="10">
+      <c r="G58">
         <f>'d1456 #2'!F5</f>
         <v>3.9000000000000004</v>
       </c>
-      <c r="H58" s="10">
+      <c r="H58">
         <v>4</v>
       </c>
       <c r="I58">
@@ -2418,29 +2417,29 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="10" t="s">
+      <c r="A59" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" t="s">
         <v>4</v>
       </c>
       <c r="E59">
         <v>2995</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F59">
         <v>17.670000000000002</v>
       </c>
-      <c r="G59" s="10">
+      <c r="G59">
         <f>'d1456 #2'!F6</f>
         <v>4</v>
       </c>
-      <c r="H59" s="10">
+      <c r="H59">
         <v>4.05</v>
       </c>
       <c r="I59">
@@ -2449,29 +2448,29 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="10" t="s">
+      <c r="A60" t="s">
         <v>18</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" t="s">
         <v>20</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" t="s">
         <v>23</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" t="s">
         <v>5</v>
       </c>
       <c r="E60">
         <v>7694</v>
       </c>
-      <c r="F60" s="10">
+      <c r="F60">
         <v>22.4</v>
       </c>
-      <c r="G60" s="10">
+      <c r="G60">
         <f>'d1456 #2'!F7</f>
         <v>3.1999999999999997</v>
       </c>
-      <c r="H60" s="10">
+      <c r="H60">
         <v>3.25</v>
       </c>
       <c r="I60">
@@ -2480,29 +2479,29 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="10" t="s">
+      <c r="A61" t="s">
         <v>18</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" t="s">
         <v>6</v>
       </c>
       <c r="E61">
         <v>8407</v>
       </c>
-      <c r="F61" s="10">
+      <c r="F61">
         <v>22.76</v>
       </c>
-      <c r="G61" s="10">
+      <c r="G61">
         <f>'d1456 #2'!F8</f>
         <v>4.2</v>
       </c>
-      <c r="H61" s="10">
+      <c r="H61">
         <v>4.0999999999999996</v>
       </c>
       <c r="I61">
@@ -2511,29 +2510,29 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="10" t="s">
+      <c r="A62" t="s">
         <v>18</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" t="s">
         <v>23</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" t="s">
         <v>4</v>
       </c>
       <c r="E62">
         <v>2954</v>
       </c>
-      <c r="F62" s="10">
+      <c r="F62">
         <v>22.56</v>
       </c>
-      <c r="G62" s="10">
+      <c r="G62">
         <f>'d1456 #2'!F9</f>
         <v>3.65</v>
       </c>
-      <c r="H62" s="10">
+      <c r="H62">
         <v>3.55</v>
       </c>
       <c r="I62">
@@ -2542,29 +2541,29 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="10" t="s">
+      <c r="A63" t="s">
         <v>18</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" t="s">
         <v>21</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" t="s">
         <v>23</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" t="s">
         <v>5</v>
       </c>
       <c r="E63">
         <v>7476</v>
       </c>
-      <c r="F63" s="10">
+      <c r="F63">
         <v>35.4</v>
       </c>
-      <c r="G63" s="10">
+      <c r="G63">
         <f>'d1456 #2'!F10</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H63" s="10">
+      <c r="H63">
         <v>4.0999999999999996</v>
       </c>
       <c r="I63">
@@ -2573,29 +2572,29 @@
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="10" t="s">
+      <c r="A64" t="s">
         <v>18</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" t="s">
         <v>21</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C64" t="s">
         <v>23</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="D64" t="s">
         <v>6</v>
       </c>
       <c r="E64">
         <v>8170</v>
       </c>
-      <c r="F64" s="10">
+      <c r="F64">
         <v>25.67</v>
       </c>
-      <c r="G64" s="10">
+      <c r="G64">
         <f>'d1456 #2'!F11</f>
         <v>3.65</v>
       </c>
-      <c r="H64" s="10">
+      <c r="H64">
         <v>3.55</v>
       </c>
       <c r="I64">
@@ -2604,29 +2603,29 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="10" t="s">
+      <c r="A65" t="s">
         <v>34</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" t="s">
         <v>19</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C65" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" t="s">
         <v>4</v>
       </c>
       <c r="E65">
         <v>3730</v>
       </c>
-      <c r="F65" s="10">
+      <c r="F65">
         <v>264.14</v>
       </c>
-      <c r="G65" s="10">
+      <c r="G65">
         <f>'d3235 #2'!F3</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H65" s="10">
+      <c r="H65">
         <v>4.0999999999999996</v>
       </c>
       <c r="I65">
@@ -2635,29 +2634,29 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="10" t="s">
+      <c r="A66" t="s">
         <v>34</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" t="s">
         <v>23</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="E66">
         <v>9489</v>
       </c>
-      <c r="F66" s="10">
+      <c r="F66">
         <v>64.040000000000006</v>
       </c>
-      <c r="G66" s="10">
+      <c r="G66">
         <f>'d3235 #2'!F4</f>
         <v>3.65</v>
       </c>
-      <c r="H66" s="10">
+      <c r="H66">
         <v>3.55</v>
       </c>
       <c r="I66">
@@ -2666,326 +2665,326 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="10" t="s">
+      <c r="A67" t="s">
         <v>34</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C67" t="s">
         <v>23</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" t="s">
         <v>6</v>
       </c>
       <c r="E67">
         <v>10660</v>
       </c>
-      <c r="F67" s="10">
+      <c r="F67">
         <v>50.48</v>
       </c>
-      <c r="G67" s="10">
+      <c r="G67">
         <f>'d3235 #2'!F5</f>
         <v>3.75</v>
       </c>
-      <c r="H67" s="10">
+      <c r="H67">
         <v>3.85</v>
       </c>
       <c r="I67">
-        <f t="shared" ref="I67:I130" si="1" xml:space="preserve"> ABS(H67-G67)</f>
+        <f t="shared" ref="I67:I130" si="3" xml:space="preserve"> ABS(H67-G67)</f>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="10" t="s">
+      <c r="A68" t="s">
         <v>34</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" t="s">
         <v>20</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C68" t="s">
         <v>23</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D68" t="s">
         <v>4</v>
       </c>
       <c r="E68">
         <v>2992</v>
       </c>
-      <c r="F68" s="10">
+      <c r="F68">
         <v>17.38</v>
       </c>
-      <c r="G68" s="10">
+      <c r="G68">
         <f>'d3235 #2'!F6</f>
         <v>3.3</v>
       </c>
-      <c r="H68" s="10">
+      <c r="H68">
         <v>3.2</v>
       </c>
       <c r="I68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9.9999999999999645E-2</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="10" t="s">
+      <c r="A69" t="s">
         <v>34</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" t="s">
         <v>20</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C69" t="s">
         <v>23</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69">
         <v>7615</v>
       </c>
-      <c r="F69" s="10">
+      <c r="F69">
         <v>20.77</v>
       </c>
-      <c r="G69" s="10">
+      <c r="G69">
         <f>'d3235 #2'!F7</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H69" s="10">
+      <c r="H69">
         <v>4.0999999999999996</v>
       </c>
       <c r="I69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="10" t="s">
+      <c r="A70" t="s">
         <v>34</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" t="s">
         <v>20</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C70" t="s">
         <v>23</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="D70" t="s">
         <v>6</v>
       </c>
       <c r="E70">
         <v>8327</v>
       </c>
-      <c r="F70" s="10">
+      <c r="F70">
         <v>16.09</v>
       </c>
-      <c r="G70" s="10">
+      <c r="G70">
         <f>'d3235 #2'!F8</f>
         <v>3.9999999999999996</v>
       </c>
-      <c r="H70" s="10">
+      <c r="H70">
         <v>4.0999999999999996</v>
       </c>
       <c r="I70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="10" t="s">
+      <c r="A71" t="s">
         <v>34</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C71" t="s">
         <v>23</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" t="s">
         <v>4</v>
       </c>
       <c r="E71">
         <v>2932</v>
       </c>
-      <c r="F71" s="10">
+      <c r="F71">
         <v>26.36</v>
       </c>
-      <c r="G71" s="10">
+      <c r="G71">
         <f>'d3235 #2'!F9</f>
         <v>4.9000000000000004</v>
       </c>
-      <c r="H71" s="10">
+      <c r="H71">
         <v>5</v>
       </c>
       <c r="I71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9.9999999999999645E-2</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="10" t="s">
+      <c r="A72" t="s">
         <v>34</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C72" t="s">
         <v>23</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="E72">
         <v>7360</v>
       </c>
-      <c r="F72" s="10">
+      <c r="F72">
         <v>26.37</v>
       </c>
-      <c r="G72" s="10">
+      <c r="G72">
         <f>'d3235 #2'!F10</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H72" s="10">
+      <c r="H72">
         <v>4.0999999999999996</v>
       </c>
       <c r="I72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="10" t="s">
+      <c r="A73" t="s">
         <v>34</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" t="s">
         <v>21</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C73" t="s">
         <v>23</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D73" t="s">
         <v>6</v>
       </c>
       <c r="E73">
         <v>8053</v>
       </c>
-      <c r="F73" s="10">
+      <c r="F73">
         <v>46.65</v>
       </c>
-      <c r="G73" s="10">
+      <c r="G73">
         <f>'d3235 #2'!F11</f>
         <v>4.6500000000000004</v>
       </c>
-      <c r="H73" s="10">
+      <c r="H73">
         <v>4.6500000000000004</v>
       </c>
       <c r="I73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="10" t="s">
+      <c r="A74" t="s">
         <v>16</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" t="s">
         <v>19</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C74" t="s">
         <v>24</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" t="s">
         <v>4</v>
       </c>
       <c r="E74">
         <v>3100</v>
       </c>
-      <c r="F74" s="10">
+      <c r="F74">
         <v>100.74</v>
       </c>
-      <c r="G74" s="10">
+      <c r="G74">
         <f>'d131 #3'!F3</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H74" s="10">
+      <c r="H74">
         <v>4.0999999999999996</v>
       </c>
       <c r="I74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="10" t="s">
+      <c r="A75" t="s">
         <v>16</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" t="s">
         <v>19</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="C75" t="s">
         <v>24</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75">
         <v>8624</v>
       </c>
-      <c r="F75" s="10">
+      <c r="F75">
         <v>50.3</v>
       </c>
-      <c r="G75" s="10">
+      <c r="G75">
         <f>'d131 #3'!F4</f>
         <v>4.3</v>
       </c>
-      <c r="H75" s="10">
+      <c r="H75">
         <v>4.25</v>
       </c>
       <c r="I75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="10" t="s">
+      <c r="A76" t="s">
         <v>16</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B76" t="s">
         <v>19</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C76" t="s">
         <v>24</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" t="s">
         <v>6</v>
       </c>
       <c r="E76">
         <v>9079</v>
       </c>
-      <c r="F76" s="10">
+      <c r="F76">
         <v>94.9</v>
       </c>
-      <c r="G76" s="10">
+      <c r="G76">
         <f>'d131 #3'!F5</f>
         <v>4.3</v>
       </c>
-      <c r="H76" s="10">
+      <c r="H76">
         <v>4.25</v>
       </c>
       <c r="I76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="10" t="s">
+      <c r="A77" t="s">
         <v>16</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" t="s">
         <v>20</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C77" t="s">
         <v>24</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D77" t="s">
         <v>4</v>
       </c>
       <c r="E77">
@@ -2994,1437 +2993,1437 @@
       <c r="F77">
         <v>31.88</v>
       </c>
-      <c r="G77" s="10">
+      <c r="G77">
         <f>'d131 #3'!F6</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H77" s="10">
+      <c r="H77">
         <v>4.0999999999999996</v>
       </c>
       <c r="I77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="10" t="s">
+      <c r="A78" t="s">
         <v>16</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" t="s">
         <v>20</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C78" t="s">
         <v>24</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78">
         <v>7408</v>
       </c>
-      <c r="F78" s="10">
+      <c r="F78">
         <v>23.4</v>
       </c>
-      <c r="G78" s="10">
+      <c r="G78">
         <f>'d131 #3'!F7</f>
         <v>4.2</v>
       </c>
-      <c r="H78" s="10">
+      <c r="H78">
         <v>4.25</v>
       </c>
       <c r="I78">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="10" t="s">
+      <c r="A79" t="s">
         <v>16</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" t="s">
         <v>20</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C79" t="s">
         <v>24</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" t="s">
         <v>6</v>
       </c>
       <c r="E79">
         <v>7830</v>
       </c>
-      <c r="F79" s="10">
+      <c r="F79">
         <v>18.850000000000001</v>
       </c>
-      <c r="G79" s="10">
+      <c r="G79">
         <f>'d131 #3'!F8</f>
         <v>4.2</v>
       </c>
-      <c r="H79" s="10">
+      <c r="H79">
         <v>4.1500000000000004</v>
       </c>
       <c r="I79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="10" t="s">
+      <c r="A80" t="s">
         <v>16</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" t="s">
         <v>21</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" t="s">
         <v>24</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" t="s">
         <v>4</v>
       </c>
       <c r="E80">
         <v>2760</v>
       </c>
-      <c r="F80" s="10">
+      <c r="F80">
         <v>23.12</v>
       </c>
-      <c r="G80" s="10">
+      <c r="G80">
         <f>'d131 #3'!F9</f>
         <v>3.4000000000000004</v>
       </c>
-      <c r="H80" s="10">
+      <c r="H80">
         <v>3.25</v>
       </c>
       <c r="I80">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.15000000000000036</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" s="10" t="s">
+      <c r="A81" t="s">
         <v>16</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" t="s">
         <v>21</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" t="s">
         <v>24</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" t="s">
         <v>5</v>
       </c>
       <c r="E81">
         <v>7291</v>
       </c>
-      <c r="F81" s="10">
+      <c r="F81">
         <v>55.51</v>
       </c>
-      <c r="G81" s="10">
+      <c r="G81">
         <f>'d131 #3'!F10</f>
         <v>3.8499999999999996</v>
       </c>
-      <c r="H81" s="10">
+      <c r="H81">
         <v>3.85</v>
       </c>
       <c r="I81">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.4408920985006262E-16</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A82" s="10" t="s">
+      <c r="A82" t="s">
         <v>16</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="D82" t="s">
         <v>6</v>
       </c>
       <c r="E82">
         <v>7705</v>
       </c>
-      <c r="F82" s="10">
+      <c r="F82">
         <v>26.2</v>
       </c>
-      <c r="G82" s="10">
+      <c r="G82">
         <f>'d131 #3'!F11</f>
         <v>4.75</v>
       </c>
-      <c r="H82" s="10">
+      <c r="H82">
         <v>4.75</v>
       </c>
       <c r="I82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" s="10" t="s">
+      <c r="A83" t="s">
         <v>33</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" t="s">
         <v>24</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D83" t="s">
         <v>4</v>
       </c>
       <c r="E83">
         <v>2624</v>
       </c>
-      <c r="F83" s="10">
+      <c r="F83">
         <v>50.53</v>
       </c>
-      <c r="G83" s="10">
+      <c r="G83">
         <f>'d393 #3'!F3</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H83" s="10">
+      <c r="H83">
         <v>4.2</v>
       </c>
       <c r="I83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" s="10" t="s">
+      <c r="A84" t="s">
         <v>33</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" t="s">
         <v>19</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" t="s">
         <v>24</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84">
         <v>6629</v>
       </c>
-      <c r="F84" s="10">
+      <c r="F84">
         <v>939.74</v>
       </c>
-      <c r="G84" s="10">
+      <c r="G84">
         <f>'d393 #3'!F4</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="H84" s="10">
+      <c r="H84">
         <v>4.1500000000000004</v>
       </c>
       <c r="I84">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999998934E-2</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A85" s="10" t="s">
+      <c r="A85" t="s">
         <v>33</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" t="s">
         <v>19</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C85" t="s">
         <v>24</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" t="s">
         <v>6</v>
       </c>
       <c r="E85">
         <v>7014</v>
       </c>
-      <c r="F85" s="10">
+      <c r="F85">
         <v>40.619999999999997</v>
       </c>
-      <c r="G85" s="10">
+      <c r="G85">
         <f>'d393 #3'!F5</f>
         <v>4.3499999999999996</v>
       </c>
-      <c r="H85" s="10">
+      <c r="H85">
         <v>4.45</v>
       </c>
       <c r="I85">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A86" s="10" t="s">
+      <c r="A86" t="s">
         <v>33</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" t="s">
         <v>20</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C86" t="s">
         <v>24</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="D86" t="s">
         <v>4</v>
       </c>
       <c r="E86">
         <v>2361</v>
       </c>
-      <c r="F86" s="10">
+      <c r="F86">
         <v>22.95</v>
       </c>
-      <c r="G86" s="10">
+      <c r="G86">
         <f>'d393 #3'!F6</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H86" s="10">
+      <c r="H86">
         <v>4.1500000000000004</v>
       </c>
       <c r="I86">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5.0000000000000711E-2</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A87" s="10" t="s">
+      <c r="A87" t="s">
         <v>33</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" t="s">
         <v>20</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C87" t="s">
         <v>24</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87">
         <v>5748</v>
       </c>
-      <c r="F87" s="10">
+      <c r="F87">
         <v>19.8</v>
       </c>
-      <c r="G87" s="10">
+      <c r="G87">
         <f>'d393 #3'!F7</f>
         <v>3.3</v>
       </c>
-      <c r="H87" s="10">
+      <c r="H87">
         <v>3.25</v>
       </c>
       <c r="I87">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A88" s="10" t="s">
+      <c r="A88" t="s">
         <v>33</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" t="s">
         <v>20</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C88" t="s">
         <v>24</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="D88" t="s">
         <v>6</v>
       </c>
       <c r="E88">
         <v>6106</v>
       </c>
-      <c r="F88" s="10">
+      <c r="F88">
         <v>19.600000000000001</v>
       </c>
-      <c r="G88" s="10">
+      <c r="G88">
         <f>'d393 #3'!F8</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H88" s="10">
+      <c r="H88">
         <v>4.1500000000000004</v>
       </c>
       <c r="I88">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5.0000000000000711E-2</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A89" s="10" t="s">
+      <c r="A89" t="s">
         <v>33</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" t="s">
         <v>21</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C89" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="D89" t="s">
         <v>4</v>
       </c>
       <c r="E89">
         <v>2361</v>
       </c>
-      <c r="F89" s="10">
+      <c r="F89">
         <v>31.41</v>
       </c>
-      <c r="G89" s="10">
+      <c r="G89">
         <f>'d393 #3'!F9</f>
         <v>3.8499999999999996</v>
       </c>
-      <c r="H89" s="10">
+      <c r="H89">
         <v>3.85</v>
       </c>
       <c r="I89">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.4408920985006262E-16</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A90" s="10" t="s">
+      <c r="A90" t="s">
         <v>33</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" t="s">
         <v>21</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C90" t="s">
         <v>24</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="E90">
         <v>5646</v>
       </c>
-      <c r="F90" s="10">
+      <c r="F90">
         <v>24.22</v>
       </c>
-      <c r="G90" s="10">
+      <c r="G90">
         <f>'d393 #3'!F10</f>
         <v>3.5500000000000003</v>
       </c>
-      <c r="H90" s="10">
+      <c r="H90">
         <v>3.45</v>
       </c>
       <c r="I90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" s="10" t="s">
+      <c r="A91" t="s">
         <v>33</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" t="s">
         <v>21</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C91" t="s">
         <v>24</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="D91" t="s">
         <v>6</v>
       </c>
       <c r="E91">
         <v>5997</v>
       </c>
-      <c r="F91" s="10">
+      <c r="F91">
         <v>21.24</v>
       </c>
-      <c r="G91" s="10">
+      <c r="G91">
         <f>'d393 #3'!F11</f>
         <v>3.9</v>
       </c>
-      <c r="H91" s="10">
+      <c r="H91">
         <v>3.8</v>
       </c>
       <c r="I91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A92" s="10" t="s">
+      <c r="A92" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" t="s">
         <v>19</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C92" t="s">
         <v>24</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" t="s">
         <v>4</v>
       </c>
       <c r="E92">
         <v>2799</v>
       </c>
-      <c r="F92" s="10">
+      <c r="F92">
         <v>34.85</v>
       </c>
-      <c r="G92" s="10">
+      <c r="G92">
         <f>'d1456 #3'!F3</f>
         <v>4.55</v>
       </c>
-      <c r="H92" s="10">
+      <c r="H92">
         <v>4.45</v>
       </c>
       <c r="I92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9.9999999999999645E-2</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A93" s="10" t="s">
+      <c r="A93" t="s">
         <v>18</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" t="s">
         <v>19</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C93" t="s">
         <v>24</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93">
         <v>6882</v>
       </c>
-      <c r="F93" s="10">
+      <c r="F93">
         <v>93.7</v>
       </c>
-      <c r="G93" s="10">
+      <c r="G93">
         <f>'d1456 #3'!F4</f>
         <v>3.5</v>
       </c>
-      <c r="H93" s="10">
+      <c r="H93">
         <v>3.45</v>
       </c>
       <c r="I93">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" s="10" t="s">
+      <c r="A94" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B94" t="s">
         <v>19</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C94" t="s">
         <v>24</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" t="s">
         <v>6</v>
       </c>
       <c r="E94">
         <v>7258</v>
       </c>
-      <c r="F94" s="10">
+      <c r="F94">
         <v>87.11</v>
       </c>
-      <c r="G94" s="10">
+      <c r="G94">
         <f>'d1456 #3'!F5</f>
         <v>3.75</v>
       </c>
-      <c r="H94" s="10">
+      <c r="H94">
         <v>3.75</v>
       </c>
       <c r="I94">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="10" t="s">
+      <c r="A95" t="s">
         <v>18</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" t="s">
         <v>20</v>
       </c>
-      <c r="C95" s="10" t="s">
+      <c r="C95" t="s">
         <v>24</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" t="s">
         <v>4</v>
       </c>
       <c r="E95">
         <v>2479</v>
       </c>
-      <c r="F95" s="10">
+      <c r="F95">
         <v>25.45</v>
       </c>
-      <c r="G95" s="10">
+      <c r="G95">
         <f>'d1456 #3'!F6</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H95" s="10">
+      <c r="H95">
         <v>4.1500000000000004</v>
       </c>
       <c r="I95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5.0000000000000711E-2</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="10" t="s">
+      <c r="A96" t="s">
         <v>18</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" t="s">
         <v>20</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C96" t="s">
         <v>24</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96">
         <v>5919</v>
       </c>
-      <c r="F96" s="10">
+      <c r="F96">
         <v>20.5</v>
       </c>
-      <c r="G96" s="10">
+      <c r="G96">
         <f>'d1456 #3'!F7</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H96" s="10">
+      <c r="H96">
         <v>4.0999999999999996</v>
       </c>
       <c r="I96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A97" s="10" t="s">
+      <c r="A97" t="s">
         <v>18</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B97" t="s">
         <v>20</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="C97" t="s">
         <v>24</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="D97" t="s">
         <v>6</v>
       </c>
       <c r="E97">
         <v>6269</v>
       </c>
-      <c r="F97" s="10">
+      <c r="F97">
         <v>25</v>
       </c>
-      <c r="G97" s="10">
+      <c r="G97">
         <f>'d1456 #3'!F8</f>
         <v>4.2</v>
       </c>
-      <c r="H97" s="10">
+      <c r="H97">
         <v>4.1500000000000004</v>
       </c>
       <c r="I97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" s="10" t="s">
+      <c r="A98" t="s">
         <v>18</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" t="s">
         <v>21</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C98" t="s">
         <v>24</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="D98" t="s">
         <v>4</v>
       </c>
       <c r="E98">
         <v>2500</v>
       </c>
-      <c r="F98" s="10">
+      <c r="F98">
         <v>33</v>
       </c>
-      <c r="G98" s="10">
+      <c r="G98">
         <f>'d1456 #3'!F9</f>
         <v>3.7499999999999996</v>
       </c>
-      <c r="H98" s="10">
+      <c r="H98">
         <v>3.65</v>
       </c>
       <c r="I98">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9.9999999999999645E-2</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A99" s="10" t="s">
+      <c r="A99" t="s">
         <v>18</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" t="s">
         <v>21</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C99" t="s">
         <v>24</v>
       </c>
-      <c r="D99" s="10" t="s">
+      <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99">
         <v>5856</v>
       </c>
-      <c r="F99" s="10">
+      <c r="F99">
         <v>39.049999999999997</v>
       </c>
-      <c r="G99" s="10">
+      <c r="G99">
         <f>'d1456 #3'!F10</f>
         <v>4.2</v>
       </c>
-      <c r="H99" s="10">
+      <c r="H99">
         <v>4.0999999999999996</v>
       </c>
       <c r="I99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="10" t="s">
+      <c r="A100" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B100" t="s">
         <v>21</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C100" t="s">
         <v>24</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="D100" t="s">
         <v>6</v>
       </c>
       <c r="E100">
         <v>6198</v>
       </c>
-      <c r="F100" s="10">
+      <c r="F100">
         <v>46.81</v>
       </c>
-      <c r="G100" s="10">
+      <c r="G100">
         <f>'d1456 #3'!F11</f>
         <v>4.2</v>
       </c>
-      <c r="H100" s="10">
+      <c r="H100">
         <v>4.0999999999999996</v>
       </c>
       <c r="I100">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="10" t="s">
+      <c r="A101" t="s">
         <v>34</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B101" t="s">
         <v>19</v>
       </c>
-      <c r="C101" s="10" t="s">
+      <c r="C101" t="s">
         <v>24</v>
       </c>
-      <c r="D101" s="10" t="s">
+      <c r="D101" t="s">
         <v>4</v>
       </c>
       <c r="E101">
         <v>2778</v>
       </c>
-      <c r="F101" s="10">
+      <c r="F101">
         <v>45.98</v>
       </c>
-      <c r="G101" s="10">
+      <c r="G101">
         <f>'d3235 #3'!F3</f>
         <v>4.3</v>
       </c>
-      <c r="H101" s="10">
+      <c r="H101">
         <v>4.25</v>
       </c>
       <c r="I101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="10" t="s">
+      <c r="A102" t="s">
         <v>34</v>
       </c>
-      <c r="B102" s="10" t="s">
+      <c r="B102" t="s">
         <v>19</v>
       </c>
-      <c r="C102" s="10" t="s">
+      <c r="C102" t="s">
         <v>24</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102">
         <v>6882</v>
       </c>
-      <c r="F102" s="10">
+      <c r="F102">
         <v>38.299999999999997</v>
       </c>
-      <c r="G102" s="10">
+      <c r="G102">
         <f>'d3235 #3'!F4</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H102" s="10">
+      <c r="H102">
         <v>3.9</v>
       </c>
       <c r="I102">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.19999999999999973</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" s="10" t="s">
+      <c r="A103" t="s">
         <v>34</v>
       </c>
-      <c r="B103" s="10" t="s">
+      <c r="B103" t="s">
         <v>19</v>
       </c>
-      <c r="C103" s="10" t="s">
+      <c r="C103" t="s">
         <v>24</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="D103" t="s">
         <v>6</v>
       </c>
       <c r="E103">
         <v>7258</v>
       </c>
-      <c r="F103" s="10">
+      <c r="F103">
         <v>262.95</v>
       </c>
-      <c r="G103" s="10">
+      <c r="G103">
         <f>'d3235 #3'!F5</f>
         <v>3.9</v>
       </c>
-      <c r="H103" s="10">
+      <c r="H103">
         <v>3.85</v>
       </c>
       <c r="I103">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="10" t="s">
+      <c r="A104" t="s">
         <v>34</v>
       </c>
-      <c r="B104" s="10" t="s">
+      <c r="B104" t="s">
         <v>20</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="C104" t="s">
         <v>24</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="D104" t="s">
         <v>4</v>
       </c>
       <c r="E104">
         <v>2485</v>
       </c>
-      <c r="F104" s="10">
+      <c r="F104">
         <v>19.46</v>
       </c>
-      <c r="G104" s="10">
+      <c r="G104">
         <f>'d3235 #3'!F6</f>
         <v>3.75</v>
       </c>
-      <c r="H104" s="10">
+      <c r="H104">
         <v>3.85</v>
       </c>
       <c r="I104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="10" t="s">
+      <c r="A105" t="s">
         <v>34</v>
       </c>
-      <c r="B105" s="10" t="s">
+      <c r="B105" t="s">
         <v>20</v>
       </c>
-      <c r="C105" s="10" t="s">
+      <c r="C105" t="s">
         <v>24</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="E105">
         <v>5968</v>
       </c>
-      <c r="F105" s="10">
+      <c r="F105">
         <v>20.11</v>
       </c>
-      <c r="G105" s="10">
+      <c r="G105">
         <f>'d3235 #3'!F7</f>
         <v>4</v>
       </c>
-      <c r="H105" s="10">
+      <c r="H105">
         <v>4.1500000000000004</v>
       </c>
       <c r="I105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.15000000000000036</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="10" t="s">
+      <c r="A106" t="s">
         <v>34</v>
       </c>
-      <c r="B106" s="10" t="s">
+      <c r="B106" t="s">
         <v>20</v>
       </c>
-      <c r="C106" s="10" t="s">
+      <c r="C106" t="s">
         <v>24</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="D106" t="s">
         <v>6</v>
       </c>
       <c r="E106">
         <v>6317</v>
       </c>
-      <c r="F106" s="10">
+      <c r="F106">
         <v>32.51</v>
       </c>
-      <c r="G106" s="10">
+      <c r="G106">
         <f>'d3235 #3'!F8</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H106" s="10">
+      <c r="H106">
         <v>4.0999999999999996</v>
       </c>
       <c r="I106">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="10" t="s">
+      <c r="A107" t="s">
         <v>34</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="B107" t="s">
         <v>21</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C107" t="s">
         <v>24</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="D107" t="s">
         <v>4</v>
       </c>
       <c r="E107">
         <v>2487</v>
       </c>
-      <c r="F107" s="10">
+      <c r="F107">
         <v>42.99</v>
       </c>
-      <c r="G107" s="10">
+      <c r="G107">
         <f>'d3235 #3'!F9</f>
         <v>4.45</v>
       </c>
-      <c r="H107" s="10">
+      <c r="H107">
         <v>4.3499999999999996</v>
       </c>
       <c r="I107">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="10" t="s">
+      <c r="A108" t="s">
         <v>34</v>
       </c>
-      <c r="B108" s="10" t="s">
+      <c r="B108" t="s">
         <v>21</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C108" t="s">
         <v>24</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="E108">
         <v>5865</v>
       </c>
-      <c r="F108" s="10">
+      <c r="F108">
         <v>60.79</v>
       </c>
-      <c r="G108" s="10">
+      <c r="G108">
         <f>'d3235 #3'!F10</f>
         <v>4.45</v>
       </c>
-      <c r="H108" s="10">
+      <c r="H108">
         <v>4.3499999999999996</v>
       </c>
       <c r="I108">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="10" t="s">
+      <c r="A109" t="s">
         <v>34</v>
       </c>
-      <c r="B109" s="10" t="s">
+      <c r="B109" t="s">
         <v>21</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="C109" t="s">
         <v>24</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="D109" t="s">
         <v>6</v>
       </c>
       <c r="E109">
         <v>6207</v>
       </c>
-      <c r="F109" s="10">
+      <c r="F109">
         <v>35.729999999999997</v>
       </c>
-      <c r="G109" s="10">
+      <c r="G109">
         <f>'d3235 #3'!F11</f>
         <v>4.3499999999999996</v>
       </c>
-      <c r="H109" s="10">
+      <c r="H109">
         <v>4.3499999999999996</v>
       </c>
       <c r="I109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="10" t="s">
+      <c r="A110" t="s">
         <v>16</v>
       </c>
-      <c r="B110" s="10" t="s">
+      <c r="B110" t="s">
         <v>19</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="C110" t="s">
         <v>25</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="D110" t="s">
         <v>4</v>
       </c>
       <c r="E110">
         <v>1915</v>
       </c>
-      <c r="F110" s="10">
+      <c r="F110">
         <v>57.88</v>
       </c>
-      <c r="G110" s="10">
+      <c r="G110">
         <f>'d131 #4'!F3</f>
         <v>2.85</v>
       </c>
-      <c r="H110" s="10">
+      <c r="H110">
         <v>2.8</v>
       </c>
       <c r="I110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5.0000000000000266E-2</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="10" t="s">
+      <c r="A111" t="s">
         <v>16</v>
       </c>
-      <c r="B111" s="10" t="s">
+      <c r="B111" t="s">
         <v>19</v>
       </c>
-      <c r="C111" s="10" t="s">
+      <c r="C111" t="s">
         <v>25</v>
       </c>
-      <c r="D111" s="10" t="s">
+      <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="E111">
         <v>4372</v>
       </c>
-      <c r="F111" s="10">
+      <c r="F111">
         <v>56.42</v>
       </c>
-      <c r="G111" s="10">
+      <c r="G111">
         <f>'d131 #4'!F4</f>
         <v>3.4999999999999996</v>
       </c>
-      <c r="H111" s="10">
+      <c r="H111">
         <v>3.35</v>
       </c>
       <c r="I111">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.14999999999999947</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="10" t="s">
+      <c r="A112" t="s">
         <v>16</v>
       </c>
-      <c r="B112" s="10" t="s">
+      <c r="B112" t="s">
         <v>19</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="C112" t="s">
         <v>25</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="D112" t="s">
         <v>6</v>
       </c>
       <c r="E112">
         <v>4408</v>
       </c>
-      <c r="F112" s="10">
+      <c r="F112">
         <v>50.6</v>
       </c>
-      <c r="G112" s="10">
+      <c r="G112">
         <f>'d131 #4'!F5</f>
         <v>3.3000000000000003</v>
       </c>
-      <c r="H112" s="10">
+      <c r="H112">
         <v>3.2</v>
       </c>
       <c r="I112">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A113" s="10" t="s">
+      <c r="A113" t="s">
         <v>16</v>
       </c>
-      <c r="B113" s="10" t="s">
+      <c r="B113" t="s">
         <v>21</v>
       </c>
-      <c r="C113" s="10" t="s">
+      <c r="C113" t="s">
         <v>25</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="D113" t="s">
         <v>4</v>
       </c>
       <c r="E113">
         <v>3493</v>
       </c>
-      <c r="F113" s="10">
+      <c r="F113">
         <v>56.82</v>
       </c>
-      <c r="G113" s="10">
+      <c r="G113">
         <f>'d131 #4'!F6</f>
         <v>3.5999999999999996</v>
       </c>
-      <c r="H113" s="10">
+      <c r="H113">
         <v>3.6</v>
       </c>
       <c r="I113">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.4408920985006262E-16</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A114" s="10" t="s">
+      <c r="A114" t="s">
         <v>16</v>
       </c>
-      <c r="B114" s="10" t="s">
+      <c r="B114" t="s">
         <v>21</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="C114" t="s">
         <v>25</v>
       </c>
-      <c r="D114" s="10" t="s">
+      <c r="D114" t="s">
         <v>5</v>
       </c>
       <c r="E114">
         <v>6497</v>
       </c>
-      <c r="F114" s="10">
+      <c r="F114">
         <v>84.36</v>
       </c>
-      <c r="G114" s="10">
+      <c r="G114">
         <f>'d131 #4'!F7</f>
         <v>4.2</v>
       </c>
-      <c r="H114" s="10">
+      <c r="H114">
         <v>4.0999999999999996</v>
       </c>
       <c r="I114">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A115" s="10" t="s">
+      <c r="A115" t="s">
         <v>16</v>
       </c>
-      <c r="B115" s="10" t="s">
+      <c r="B115" t="s">
         <v>21</v>
       </c>
-      <c r="C115" s="10" t="s">
+      <c r="C115" t="s">
         <v>25</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="D115" t="s">
         <v>6</v>
       </c>
       <c r="E115">
         <v>7433</v>
       </c>
-      <c r="F115" s="10">
+      <c r="F115">
         <v>27.18</v>
       </c>
-      <c r="G115" s="10">
+      <c r="G115">
         <f>'d131 #4'!F8</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="H115" s="10">
+      <c r="H115">
         <v>4.4000000000000004</v>
       </c>
       <c r="I115">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A116" s="10" t="s">
+      <c r="A116" t="s">
         <v>33</v>
       </c>
-      <c r="B116" s="10" t="s">
+      <c r="B116" t="s">
         <v>19</v>
       </c>
-      <c r="C116" s="10" t="s">
+      <c r="C116" t="s">
         <v>25</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="D116" t="s">
         <v>4</v>
       </c>
       <c r="E116">
         <v>1782</v>
       </c>
-      <c r="F116" s="10">
+      <c r="F116">
         <v>48.72</v>
       </c>
-      <c r="G116" s="10">
+      <c r="G116">
         <f>'d393 #4'!F3</f>
         <v>3.3000000000000003</v>
       </c>
-      <c r="H116" s="10">
+      <c r="H116">
         <v>3.35</v>
       </c>
       <c r="I116">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A117" s="10" t="s">
+      <c r="A117" t="s">
         <v>33</v>
       </c>
-      <c r="B117" s="10" t="s">
+      <c r="B117" t="s">
         <v>19</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="C117" t="s">
         <v>25</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="D117" t="s">
         <v>5</v>
       </c>
       <c r="E117">
         <v>3657</v>
       </c>
-      <c r="F117" s="10">
+      <c r="F117">
         <v>44.88</v>
       </c>
-      <c r="G117" s="10">
+      <c r="G117">
         <f>'d393 #4'!F4</f>
         <v>4.3</v>
       </c>
-      <c r="H117" s="10">
+      <c r="H117">
         <v>4.25</v>
       </c>
       <c r="I117">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" s="10" t="s">
+      <c r="A118" t="s">
         <v>33</v>
       </c>
-      <c r="B118" s="10" t="s">
+      <c r="B118" t="s">
         <v>19</v>
       </c>
-      <c r="C118" s="10" t="s">
+      <c r="C118" t="s">
         <v>25</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="D118" t="s">
         <v>6</v>
       </c>
       <c r="E118">
         <v>3693</v>
       </c>
-      <c r="F118" s="10">
+      <c r="F118">
         <v>49.4</v>
       </c>
-      <c r="G118" s="10">
+      <c r="G118">
         <f>'d393 #4'!F5</f>
         <v>3.2</v>
       </c>
-      <c r="H118" s="10">
+      <c r="H118">
         <v>3.25</v>
       </c>
       <c r="I118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119" s="10" t="s">
+      <c r="A119" t="s">
         <v>33</v>
       </c>
-      <c r="B119" s="10" t="s">
+      <c r="B119" t="s">
         <v>21</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="C119" t="s">
         <v>25</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="D119" t="s">
         <v>4</v>
       </c>
       <c r="E119">
         <v>3433</v>
       </c>
-      <c r="F119" s="10">
+      <c r="F119">
         <v>33.49</v>
       </c>
-      <c r="G119" s="10">
+      <c r="G119">
         <f>'d393 #4'!F6</f>
         <v>3.9999999999999996</v>
       </c>
-      <c r="H119" s="10">
+      <c r="H119">
         <v>4.0999999999999996</v>
       </c>
       <c r="I119">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" s="10" t="s">
+      <c r="A120" t="s">
         <v>33</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="B120" t="s">
         <v>21</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C120" t="s">
         <v>25</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D120" t="s">
         <v>5</v>
       </c>
       <c r="E120">
         <v>5989</v>
       </c>
-      <c r="F120" s="10">
+      <c r="F120">
         <v>36.31</v>
       </c>
-      <c r="G120" s="10">
+      <c r="G120">
         <f>'d393 #4'!F7</f>
         <v>4.2</v>
       </c>
-      <c r="H120" s="10">
+      <c r="H120">
         <v>4.0999999999999996</v>
       </c>
       <c r="I120">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" s="10" t="s">
+      <c r="A121" t="s">
         <v>33</v>
       </c>
-      <c r="B121" s="10" t="s">
+      <c r="B121" t="s">
         <v>21</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C121" t="s">
         <v>25</v>
       </c>
-      <c r="D121" s="10" t="s">
+      <c r="D121" t="s">
         <v>6</v>
       </c>
       <c r="E121">
         <v>6950</v>
       </c>
-      <c r="F121" s="10">
+      <c r="F121">
         <v>21.82</v>
       </c>
-      <c r="G121" s="10">
+      <c r="G121">
         <f>'d393 #4'!F8</f>
         <v>4.2</v>
       </c>
-      <c r="H121" s="10">
+      <c r="H121">
         <v>4.0999999999999996</v>
       </c>
       <c r="I121">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122" s="10" t="s">
+      <c r="A122" t="s">
         <v>18</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B122" t="s">
         <v>19</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C122" t="s">
         <v>25</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" t="s">
         <v>4</v>
       </c>
       <c r="E122">
         <v>1798</v>
       </c>
-      <c r="F122" s="10">
+      <c r="F122">
         <v>41.41</v>
       </c>
-      <c r="G122" s="10">
+      <c r="G122">
         <f>'d1456 #4'!F3</f>
         <v>3.4</v>
       </c>
-      <c r="H122" s="10">
+      <c r="H122">
         <v>3.25</v>
       </c>
       <c r="I122">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.14999999999999991</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123" s="10" t="s">
+      <c r="A123" t="s">
         <v>18</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B123" t="s">
         <v>19</v>
       </c>
-      <c r="C123" s="10" t="s">
+      <c r="C123" t="s">
         <v>25</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123">
         <v>3676</v>
       </c>
-      <c r="F123" s="10">
+      <c r="F123">
         <v>77.739999999999995</v>
       </c>
-      <c r="G123" s="10">
+      <c r="G123">
         <f>'d1456 #4'!F4</f>
         <v>4</v>
       </c>
-      <c r="H123" s="10">
+      <c r="H123">
         <v>4</v>
       </c>
       <c r="I123">
@@ -4433,60 +4432,60 @@
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" s="10" t="s">
+      <c r="A124" t="s">
         <v>18</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="B124" t="s">
         <v>19</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C124" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="D124" t="s">
         <v>6</v>
       </c>
       <c r="E124">
         <v>3713</v>
       </c>
-      <c r="F124" s="10">
+      <c r="F124">
         <v>55.91</v>
       </c>
-      <c r="G124" s="10">
+      <c r="G124">
         <f>'d1456 #4'!F5</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="H124" s="10">
+      <c r="H124">
         <v>4.2</v>
       </c>
       <c r="I124">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8.8817841970012523E-16</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" s="10" t="s">
+      <c r="A125" t="s">
         <v>18</v>
       </c>
-      <c r="B125" s="10" t="s">
+      <c r="B125" t="s">
         <v>21</v>
       </c>
-      <c r="C125" s="10" t="s">
+      <c r="C125" t="s">
         <v>25</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D125" t="s">
         <v>4</v>
       </c>
       <c r="E125">
         <v>3402</v>
       </c>
-      <c r="F125" s="10">
+      <c r="F125">
         <v>32.159999999999997</v>
       </c>
-      <c r="G125" s="10">
+      <c r="G125">
         <f>'d1456 #4'!F6</f>
         <v>4.0999999999999996</v>
       </c>
-      <c r="H125" s="10">
+      <c r="H125">
         <v>4.1500000000000004</v>
       </c>
       <c r="I125">
@@ -4495,171 +4494,171 @@
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="10" t="s">
+      <c r="A126" t="s">
         <v>18</v>
       </c>
-      <c r="B126" s="10" t="s">
+      <c r="B126" t="s">
         <v>21</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="C126" t="s">
         <v>25</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126">
         <v>5919</v>
       </c>
-      <c r="F126" s="10">
+      <c r="F126">
         <v>40.380000000000003</v>
       </c>
-      <c r="G126" s="10">
+      <c r="G126">
         <f>'d1456 #4'!F7</f>
         <v>4.45</v>
       </c>
-      <c r="H126" s="10">
+      <c r="H126">
         <v>4.3499999999999996</v>
       </c>
       <c r="I126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="10" t="s">
+      <c r="A127" t="s">
         <v>18</v>
       </c>
-      <c r="B127" s="10" t="s">
+      <c r="B127" t="s">
         <v>21</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C127" t="s">
         <v>25</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="D127" t="s">
         <v>6</v>
       </c>
       <c r="E127">
         <v>6856</v>
       </c>
-      <c r="F127" s="10">
+      <c r="F127">
         <v>35.9</v>
       </c>
-      <c r="G127" s="10">
+      <c r="G127">
         <f>'d1456 #4'!F8</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="H127" s="10">
+      <c r="H127">
         <v>4.45</v>
       </c>
       <c r="I127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.9999999999999822E-2</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="10" t="s">
+      <c r="A128" t="s">
         <v>34</v>
       </c>
-      <c r="B128" s="10" t="s">
+      <c r="B128" t="s">
         <v>19</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C128" t="s">
         <v>25</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="D128" t="s">
         <v>4</v>
       </c>
       <c r="E128">
         <v>1802</v>
       </c>
-      <c r="F128" s="10">
+      <c r="F128">
         <v>54.22</v>
       </c>
       <c r="G128">
         <f>'d3235 #4'!F3</f>
         <v>3.1</v>
       </c>
-      <c r="H128" s="10">
+      <c r="H128">
         <v>3</v>
       </c>
       <c r="I128">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A129" s="10" t="s">
+      <c r="A129" t="s">
         <v>34</v>
       </c>
-      <c r="B129" s="10" t="s">
+      <c r="B129" t="s">
         <v>19</v>
       </c>
-      <c r="C129" s="10" t="s">
+      <c r="C129" t="s">
         <v>25</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129">
         <v>3785</v>
       </c>
-      <c r="F129" s="10">
+      <c r="F129">
         <v>48.45</v>
       </c>
       <c r="G129">
         <f>'d3235 #4'!F4</f>
         <v>3.1999999999999997</v>
       </c>
-      <c r="H129" s="10">
+      <c r="H129">
         <v>3.25</v>
       </c>
       <c r="I129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5.0000000000000266E-2</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A130" s="10" t="s">
+      <c r="A130" t="s">
         <v>34</v>
       </c>
-      <c r="B130" s="10" t="s">
+      <c r="B130" t="s">
         <v>19</v>
       </c>
-      <c r="C130" s="10" t="s">
+      <c r="C130" t="s">
         <v>25</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="D130" t="s">
         <v>6</v>
       </c>
       <c r="E130">
         <v>3822</v>
       </c>
-      <c r="F130" s="10">
+      <c r="F130">
         <v>60.01</v>
       </c>
       <c r="G130">
         <f>'d3235 #4'!F5</f>
         <v>3.5500000000000003</v>
       </c>
-      <c r="H130" s="10">
+      <c r="H130">
         <v>3.55</v>
       </c>
       <c r="I130">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.4408920985006262E-16</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A131" s="10" t="s">
+      <c r="A131" t="s">
         <v>34</v>
       </c>
-      <c r="B131" s="10" t="s">
+      <c r="B131" t="s">
         <v>21</v>
       </c>
-      <c r="C131" s="10" t="s">
+      <c r="C131" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="10" t="s">
+      <c r="D131" t="s">
         <v>4</v>
       </c>
       <c r="E131">
@@ -4676,21 +4675,21 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="I131">
-        <f t="shared" ref="I131:I133" si="2" xml:space="preserve"> ABS(H131-G131)</f>
+        <f t="shared" ref="I131:I133" si="4" xml:space="preserve"> ABS(H131-G131)</f>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A132" s="10" t="s">
+      <c r="A132" t="s">
         <v>34</v>
       </c>
-      <c r="B132" s="10" t="s">
+      <c r="B132" t="s">
         <v>21</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="C132" t="s">
         <v>25</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132">
@@ -4707,21 +4706,21 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="I132">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.10000000000000053</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A133" s="10" t="s">
+      <c r="A133" t="s">
         <v>34</v>
       </c>
-      <c r="B133" s="10" t="s">
+      <c r="B133" t="s">
         <v>21</v>
       </c>
-      <c r="C133" s="10" t="s">
+      <c r="C133" t="s">
         <v>25</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="D133" t="s">
         <v>6</v>
       </c>
       <c r="E133">
@@ -4738,7 +4737,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="I133">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -4774,7 +4773,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -6198,7 +6197,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -7622,7 +7621,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -9046,7 +9045,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -10470,7 +10469,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -11894,7 +11893,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -12857,7 +12856,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -13820,7 +13819,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -14783,7 +14782,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -15746,7 +15745,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -17170,7 +17169,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -18594,7 +18593,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -20018,7 +20017,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -21442,7 +21441,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -22866,7 +22865,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
@@ -24290,7 +24289,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="7"/>
